--- a/products/meta-ads-tracking-template.xlsx
+++ b/products/meta-ads-tracking-template.xlsx
@@ -2557,7 +2557,7 @@
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>Free 15-point audit checklist + fixed-price done-for-you audit: DM @GalaxySportsAI on X. (c) 2026 Garrett Baxley - Signal Origin. Personal/internal business use; no resale.</t>
+          <t>Free 15-point audit checklist + fixed-price done-for-you audit: x.com/SignaL_OriginHQ (email Baxley.Garrett@gmail.com or DM "audit"). (c) 2026 Garrett Baxley - Signal Origin. Personal/internal business use; no resale.</t>
         </is>
       </c>
     </row>
